--- a/docs/downloads/04/tbl_raison_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_raison_alaotra_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -397,12 +397,6 @@
           <t>Mariage</t>
         </is>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>3.2</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -535,12 +529,6 @@
           <t>Travail agricole</t>
         </is>
       </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8">
-        <v>13.8</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -558,12 +546,6 @@
           <t>Travail non agricole</t>
         </is>
       </c>
-      <c r="D9">
-        <v>3</v>
-      </c>
-      <c r="E9">
-        <v>10.3</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -581,12 +563,6 @@
           <t>Mariage</t>
         </is>
       </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-      <c r="E10">
-        <v>4.4</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,12 +787,6 @@
           <t>Travail agricole</t>
         </is>
       </c>
-      <c r="D20">
-        <v>2</v>
-      </c>
-      <c r="E20">
-        <v>3.4</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -880,12 +850,6 @@
           <t>Travail agricole</t>
         </is>
       </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23">
-        <v>2.6</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -903,12 +867,6 @@
           <t>Mariage</t>
         </is>
       </c>
-      <c r="D24">
-        <v>3</v>
-      </c>
-      <c r="E24">
-        <v>5.8</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -949,12 +907,6 @@
           <t>Travail agricole</t>
         </is>
       </c>
-      <c r="D26">
-        <v>4</v>
-      </c>
-      <c r="E26">
-        <v>7.7</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1041,12 +993,6 @@
           <t>Travail agricole</t>
         </is>
       </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-      <c r="E30">
-        <v>2.8</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1064,12 +1010,6 @@
           <t>Travail non agricole</t>
         </is>
       </c>
-      <c r="D31">
-        <v>2</v>
-      </c>
-      <c r="E31">
-        <v>5.6</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1156,12 +1096,6 @@
           <t>Travail non agricole</t>
         </is>
       </c>
-      <c r="D35">
-        <v>2</v>
-      </c>
-      <c r="E35">
-        <v>4.3</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1225,12 +1159,6 @@
           <t>Travail agricole</t>
         </is>
       </c>
-      <c r="D38">
-        <v>3</v>
-      </c>
-      <c r="E38">
-        <v>9.1</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1248,12 +1176,6 @@
           <t>Travail non agricole</t>
         </is>
       </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="E39">
-        <v>3</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1268,14 +1190,8 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Accès terre</t>
-        </is>
-      </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-      <c r="E40">
-        <v>1.1</v>
+          <t>Autre raison</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -1291,14 +1207,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Autre</t>
+          <t>Mariage</t>
         </is>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E41">
-        <v>1.1</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="42">
@@ -1314,14 +1230,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Natif</t>
         </is>
       </c>
       <c r="D42">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="E42">
-        <v>13.3</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -1337,14 +1253,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Travail agricole</t>
         </is>
       </c>
       <c r="D43">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="E43">
-        <v>75.59999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="44">
@@ -1360,14 +1276,8 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D44">
-        <v>7</v>
-      </c>
-      <c r="E44">
-        <v>7.8</v>
+          <t>Travail non agricole</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -1378,19 +1288,13 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-      <c r="E45">
-        <v>1.1</v>
+          <t>Autre raison</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -1406,14 +1310,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Accès terre</t>
+          <t>Mariage</t>
         </is>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E46">
-        <v>1.6</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="47">
@@ -1429,14 +1333,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Natif</t>
         </is>
       </c>
       <c r="D47">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E47">
-        <v>41.3</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="48">
@@ -1452,14 +1356,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Travail agricole</t>
         </is>
       </c>
       <c r="D48">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E48">
-        <v>47.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="49">
@@ -1475,37 +1379,25 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D49">
-        <v>5</v>
-      </c>
-      <c r="E49">
-        <v>7.9</v>
+          <t>Travail non agricole</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-      <c r="E50">
-        <v>1.6</v>
+          <t>Autre raison</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -1567,14 +1459,8 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Suivi famille</t>
-        </is>
-      </c>
-      <c r="D53">
-        <v>1</v>
-      </c>
-      <c r="E53">
-        <v>1.1</v>
+          <t>Travail agricole</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -1590,14 +1476,8 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D54">
-        <v>3</v>
-      </c>
-      <c r="E54">
-        <v>3.4</v>
+          <t>Travail non agricole</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -1608,19 +1488,13 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D55">
-        <v>1</v>
-      </c>
-      <c r="E55">
-        <v>1.1</v>
+          <t>Autre raison</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -1682,14 +1556,8 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Suivi famille</t>
-        </is>
-      </c>
-      <c r="D58">
-        <v>1</v>
-      </c>
-      <c r="E58">
-        <v>1.5</v>
+          <t>Travail agricole</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -1705,37 +1573,31 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D59">
-        <v>3</v>
-      </c>
-      <c r="E59">
-        <v>4.4</v>
+          <t>Travail non agricole</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
+          <t>Mariage</t>
         </is>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E60">
-        <v>1.5</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="61">
@@ -1751,14 +1613,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Natif</t>
         </is>
       </c>
       <c r="D61">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="E61">
-        <v>13.7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62">
@@ -1774,14 +1636,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Travail agricole</t>
         </is>
       </c>
       <c r="D62">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="E62">
-        <v>74</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -1797,14 +1659,8 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D63">
-        <v>6</v>
-      </c>
-      <c r="E63">
-        <v>8.199999999999999</v>
+          <t>Travail non agricole</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -1815,19 +1671,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
+          <t>Mariage</t>
         </is>
       </c>
       <c r="D64">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E64">
-        <v>4.1</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="65">
@@ -1843,14 +1699,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Natif</t>
         </is>
       </c>
       <c r="D65">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E65">
-        <v>33.3</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="66">
@@ -1866,14 +1722,8 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D66">
-        <v>31</v>
-      </c>
-      <c r="E66">
-        <v>60.8</v>
+          <t>Travail agricole</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -1889,37 +1739,25 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D67">
-        <v>2</v>
-      </c>
-      <c r="E67">
-        <v>3.9</v>
+          <t>Travail non agricole</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D68">
-        <v>1</v>
-      </c>
-      <c r="E68">
-        <v>2</v>
+          <t>Autre raison</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -1935,14 +1773,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Accès terre</t>
+          <t>Mariage</t>
         </is>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="E69">
-        <v>0.2</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="70">
@@ -1958,14 +1796,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Autre</t>
+          <t>Natif</t>
         </is>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>371</v>
       </c>
       <c r="E70">
-        <v>0.2</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="71">
@@ -1981,14 +1819,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Travail agricole</t>
         </is>
       </c>
       <c r="D71">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E71">
-        <v>10.1</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="72">
@@ -2004,14 +1842,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Travail non agricole</t>
         </is>
       </c>
       <c r="D72">
-        <v>371</v>
+        <v>35</v>
       </c>
       <c r="E72">
-        <v>73.3</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="73">
@@ -2022,19 +1860,13 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Suivi famille</t>
-        </is>
-      </c>
-      <c r="D73">
-        <v>1</v>
-      </c>
-      <c r="E73">
-        <v>0.2</v>
+          <t>Autre raison</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -2045,19 +1877,19 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
+          <t>Mariage</t>
         </is>
       </c>
       <c r="D74">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="E74">
-        <v>9.1</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="75">
@@ -2068,19 +1900,19 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
+          <t>Natif</t>
         </is>
       </c>
       <c r="D75">
-        <v>35</v>
+        <v>216</v>
       </c>
       <c r="E75">
-        <v>6.9</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="76">
@@ -2096,14 +1928,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Accès terre</t>
+          <t>Travail agricole</t>
         </is>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E76">
-        <v>0.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="77">
@@ -2119,105 +1951,13 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Travail non agricole</t>
         </is>
       </c>
       <c r="D77">
-        <v>113</v>
+        <v>15</v>
       </c>
       <c r="E77">
-        <v>30.5</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D78">
-        <v>216</v>
-      </c>
-      <c r="E78">
-        <v>58.2</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Suivi famille</t>
-        </is>
-      </c>
-      <c r="D79">
-        <v>1</v>
-      </c>
-      <c r="E79">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D80">
-        <v>25</v>
-      </c>
-      <c r="E80">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D81">
-        <v>15</v>
-      </c>
-      <c r="E81">
         <v>4</v>
       </c>
     </row>

--- a/docs/downloads/04/tbl_raison_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_raison_alaotra_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,8 +394,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mariage</t>
-        </is>
+          <t>Sociale (naissance, mariage, famille)</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>25</v>
+      </c>
+      <c r="E2">
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -411,14 +417,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Économique (travail, ressources)</t>
         </is>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>51.6</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="4">
@@ -429,19 +435,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
+          <t>Sociale (naissance, mariage, famille)</t>
         </is>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>19.4</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="5">
@@ -452,71 +458,65 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>8</v>
-      </c>
-      <c r="E5">
-        <v>25.8</v>
+          <t>Économique (travail, ressources)</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Alaotra - Ambatomanga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Sociale (naissance, mariage, famille)</t>
         </is>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="E6">
-        <v>34.5</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Alaotra - Ambatomanga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Économique (travail, ressources)</t>
         </is>
       </c>
       <c r="D7">
         <v>12</v>
       </c>
       <c r="E7">
-        <v>41.4</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Alaotra - Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -526,14 +526,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
-        </is>
+          <t>Sociale (naissance, mariage, famille)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>47</v>
+      </c>
+      <c r="E8">
+        <v>88.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Alaotra - Ambatomanga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -543,14 +549,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
-        </is>
+          <t>Économique (travail, ressources)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>6</v>
+      </c>
+      <c r="E9">
+        <v>11.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -560,14 +572,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mariage</t>
-        </is>
+          <t>Sociale (naissance, mariage, famille)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>56</v>
+      </c>
+      <c r="E10">
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -577,112 +595,94 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>42</v>
-      </c>
-      <c r="E11">
-        <v>61.8</v>
+          <t>Économique (travail, ressources)</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
+          <t>Sociale (naissance, mariage, famille)</t>
         </is>
       </c>
       <c r="D12">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="E12">
-        <v>17.6</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>11</v>
-      </c>
-      <c r="E13">
-        <v>16.2</v>
+          <t>Économique (travail, ressources)</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Sociale (naissance, mariage, famille)</t>
         </is>
       </c>
       <c r="D14">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="E14">
-        <v>20.8</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>30</v>
-      </c>
-      <c r="E15">
-        <v>56.6</v>
+          <t>Économique (travail, ressources)</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -692,20 +692,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
+          <t>Sociale (naissance, mariage, famille)</t>
         </is>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="E16">
-        <v>11.3</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -715,20 +715,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>6</v>
-      </c>
-      <c r="E17">
-        <v>11.3</v>
+          <t>Économique (travail, ressources)</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -738,20 +732,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Sociale (naissance, mariage, famille)</t>
         </is>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E18">
-        <v>8.6</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -761,37 +755,43 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Économique (travail, ressources)</t>
         </is>
       </c>
       <c r="D19">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="E19">
-        <v>87.90000000000001</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
-        </is>
+          <t>Sociale (naissance, mariage, famille)</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>30</v>
+      </c>
+      <c r="E20">
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -801,60 +801,54 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>8</v>
-      </c>
-      <c r="E21">
-        <v>21.1</v>
+          <t>Économique (travail, ressources)</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>29</v>
-      </c>
-      <c r="E22">
-        <v>76.3</v>
+          <t>Autre / NSP</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
-        </is>
+          <t>Sociale (naissance, mariage, famille)</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>81</v>
+      </c>
+      <c r="E23">
+        <v>90</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -864,54 +858,66 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mariage</t>
-        </is>
+          <t>Économique (travail, ressources)</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>8</v>
+      </c>
+      <c r="E24">
+        <v>8.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Sociale (naissance, mariage, famille)</t>
         </is>
       </c>
       <c r="D25">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="E25">
-        <v>69.2</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
-        </is>
+          <t>Économique (travail, ressources)</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>6</v>
+      </c>
+      <c r="E26">
+        <v>9.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -921,66 +927,54 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>9</v>
-      </c>
-      <c r="E27">
-        <v>17.3</v>
+          <t>Conjoncturelle (écologie, insécurité)</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mariage</t>
+          <t>Sociale (naissance, mariage, famille)</t>
         </is>
       </c>
       <c r="D28">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="E28">
-        <v>27.8</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>23</v>
-      </c>
-      <c r="E29">
-        <v>63.9</v>
+          <t>Économique (travail, ressources)</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -990,14 +984,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
+          <t>Conjoncturelle (écologie, insécurité)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1007,37 +1001,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
-        </is>
+          <t>Sociale (naissance, mariage, famille)</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>64</v>
+      </c>
+      <c r="E31">
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D32">
-        <v>9</v>
-      </c>
-      <c r="E32">
-        <v>19.6</v>
+          <t>Économique (travail, ressources)</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1047,20 +1041,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Sociale (naissance, mariage, famille)</t>
         </is>
       </c>
       <c r="D33">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="E33">
-        <v>63</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1070,37 +1064,43 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
+          <t>Économique (travail, ressources)</t>
         </is>
       </c>
       <c r="D34">
         <v>6</v>
       </c>
       <c r="E34">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
-        </is>
+          <t>Sociale (naissance, mariage, famille)</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>49</v>
+      </c>
+      <c r="E35">
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1110,77 +1110,71 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D36">
-        <v>9</v>
-      </c>
-      <c r="E36">
-        <v>27.3</v>
+          <t>Économique (travail, ressources)</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D37">
-        <v>20</v>
-      </c>
-      <c r="E37">
-        <v>60.6</v>
+          <t>Autre / NSP</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
+          <t>Conjoncturelle (écologie, insécurité)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Conjoint</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Travail non agricole</t>
-        </is>
+          <t>Sociale (naissance, mariage, famille)</t>
+        </is>
+      </c>
+      <c r="D39">
+        <v>457</v>
+      </c>
+      <c r="E39">
+        <v>90.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1190,775 +1184,77 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Autre raison</t>
-        </is>
+          <t>Économique (travail, ressources)</t>
+        </is>
+      </c>
+      <c r="D40">
+        <v>47</v>
+      </c>
+      <c r="E40">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D41">
-        <v>12</v>
-      </c>
-      <c r="E41">
-        <v>13.3</v>
+          <t>Conjoncturelle (écologie, insécurité)</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Natif</t>
+          <t>Sociale (naissance, mariage, famille)</t>
         </is>
       </c>
       <c r="D42">
-        <v>68</v>
+        <v>344</v>
       </c>
       <c r="E42">
-        <v>75.59999999999999</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>Conjoint</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Travail agricole</t>
+          <t>Économique (travail, ressources)</t>
         </is>
       </c>
       <c r="D43">
+        <v>26</v>
+      </c>
+      <c r="E43">
         <v>7</v>
-      </c>
-      <c r="E43">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Alaotra - Avaradrano</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Alaotra - Avaradrano</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Autre raison</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Alaotra - Avaradrano</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D46">
-        <v>26</v>
-      </c>
-      <c r="E46">
-        <v>41.3</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Alaotra - Avaradrano</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D47">
-        <v>30</v>
-      </c>
-      <c r="E47">
-        <v>47.6</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Alaotra - Avaradrano</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D48">
-        <v>5</v>
-      </c>
-      <c r="E48">
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Alaotra - Avaradrano</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Alaotra - Feramanga Atsimo</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Autre raison</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Alaotra - Feramanga Atsimo</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D51">
-        <v>8</v>
-      </c>
-      <c r="E51">
-        <v>9.1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Alaotra - Feramanga Atsimo</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D52">
-        <v>75</v>
-      </c>
-      <c r="E52">
-        <v>85.2</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Alaotra - Feramanga Atsimo</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Alaotra - Feramanga Atsimo</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Alaotra - Feramanga Atsimo</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Autre raison</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Alaotra - Feramanga Atsimo</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D56">
-        <v>22</v>
-      </c>
-      <c r="E56">
-        <v>32.4</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Alaotra - Feramanga Atsimo</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D57">
-        <v>41</v>
-      </c>
-      <c r="E57">
-        <v>60.3</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Alaotra - Feramanga Atsimo</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Alaotra - Feramanga Atsimo</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Alaotra - Mangabe</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D60">
-        <v>10</v>
-      </c>
-      <c r="E60">
-        <v>13.7</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Alaotra - Mangabe</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D61">
-        <v>54</v>
-      </c>
-      <c r="E61">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Alaotra - Mangabe</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D62">
-        <v>6</v>
-      </c>
-      <c r="E62">
-        <v>8.199999999999999</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Alaotra - Mangabe</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Alaotra - Mangabe</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D64">
-        <v>17</v>
-      </c>
-      <c r="E64">
-        <v>33.3</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Alaotra - Mangabe</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D65">
-        <v>31</v>
-      </c>
-      <c r="E65">
-        <v>60.8</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Alaotra - Mangabe</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Alaotra - Mangabe</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Autre raison</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D69">
-        <v>51</v>
-      </c>
-      <c r="E69">
-        <v>10.1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D70">
-        <v>371</v>
-      </c>
-      <c r="E70">
-        <v>73.3</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D71">
-        <v>46</v>
-      </c>
-      <c r="E71">
-        <v>9.1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D72">
-        <v>35</v>
-      </c>
-      <c r="E72">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Autre raison</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Mariage</t>
-        </is>
-      </c>
-      <c r="D74">
-        <v>113</v>
-      </c>
-      <c r="E74">
-        <v>30.5</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Natif</t>
-        </is>
-      </c>
-      <c r="D75">
-        <v>216</v>
-      </c>
-      <c r="E75">
-        <v>58.2</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Travail agricole</t>
-        </is>
-      </c>
-      <c r="D76">
-        <v>25</v>
-      </c>
-      <c r="E76">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Conjoint</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Travail non agricole</t>
-        </is>
-      </c>
-      <c r="D77">
-        <v>15</v>
-      </c>
-      <c r="E77">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_raison_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_raison_alaotra_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -407,7 +407,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -430,7 +430,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -470,7 +470,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -516,7 +516,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -562,7 +562,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -665,7 +665,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -682,7 +682,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -722,7 +722,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -768,7 +768,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -791,7 +791,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -808,7 +808,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -825,7 +825,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -848,7 +848,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -894,7 +894,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -917,7 +917,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -934,7 +934,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -957,7 +957,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -974,7 +974,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1031,7 +1031,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1054,7 +1054,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1117,7 +1117,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1134,7 +1134,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1151,7 +1151,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1174,7 +1174,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1197,7 +1197,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1214,7 +1214,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1237,7 +1237,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
